--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -5437,7 +5437,7 @@
         <v>136398477</v>
       </c>
       <c r="B44" t="n">
-        <v>58122</v>
+        <v>58124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>136398555</v>
       </c>
       <c r="B49" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>136398547</v>
       </c>
       <c r="B50" t="n">
-        <v>57196</v>
+        <v>57198</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>136398526</v>
       </c>
       <c r="B51" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>136398522</v>
       </c>
       <c r="B52" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>136307649</v>
       </c>
       <c r="B54" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>136307714</v>
       </c>
       <c r="B55" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6129,10 +6129,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136398547</v>
+        <v>136983633</v>
       </c>
       <c r="B50" t="n">
-        <v>57198</v>
+        <v>57195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6140,33 +6140,33 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474720</v>
+        <v>474713</v>
       </c>
       <c r="R50" t="n">
-        <v>6513695</v>
+        <v>6513690</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6206,27 +6206,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Hördes i riktning mot Bastlandsmossen.</t>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6256,38 +6246,38 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136398547</t>
+          <t>https://artportalen.se/Sighting/136983633</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136398526</v>
+        <v>136398547</v>
       </c>
       <c r="B51" t="n">
-        <v>58169</v>
+        <v>57198</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6297,7 +6287,11 @@
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6353,6 +6347,11 @@
           <t>18:30</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Hördes i riktning mot Bastlandsmossen.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6380,38 +6379,38 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136398526</t>
+          <t>https://artportalen.se/Sighting/136398547</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136398522</v>
+        <v>136398526</v>
       </c>
       <c r="B52" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6504,16 +6503,16 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136398522</t>
+          <t>https://artportalen.se/Sighting/136398526</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135287667</v>
+        <v>136398522</v>
       </c>
       <c r="B53" t="n">
-        <v>57158</v>
+        <v>58164</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6521,16 +6520,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102612</v>
+        <v>103023</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6538,30 +6537,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bergsjön, Bergsjön, Vg</t>
+          <t>Mossaberget, Vg</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475000</v>
+        <v>474720</v>
       </c>
       <c r="R53" t="n">
-        <v>6512402</v>
+        <v>6513695</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6585,12 +6582,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6605,27 +6612,31 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135287667</t>
+          <t>https://artportalen.se/Sighting/136398522</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136307649</v>
+        <v>135287667</v>
       </c>
       <c r="B54" t="n">
-        <v>57186</v>
+        <v>57158</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6651,14 +6662,14 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6667,10 +6678,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475015</v>
+        <v>475000</v>
       </c>
       <c r="R54" t="n">
-        <v>6512380</v>
+        <v>6512402</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6700,19 +6711,9 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6738,41 +6739,46 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136307649</t>
+          <t>https://artportalen.se/Sighting/135287667</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136307714</v>
+        <v>136307649</v>
       </c>
       <c r="B55" t="n">
-        <v>58169</v>
+        <v>57186</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -6784,10 +6790,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475023</v>
+        <v>475015</v>
       </c>
       <c r="R55" t="n">
-        <v>6512397</v>
+        <v>6512380</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6814,22 +6820,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6855,54 +6861,59 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136307714</t>
+          <t>https://artportalen.se/Sighting/136307649</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134665086</v>
+        <v>136307714</v>
       </c>
       <c r="B56" t="n">
-        <v>99142</v>
+        <v>58169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6010639</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blodnycklar × fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta × maculata</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Olshammar, Nrk</t>
+          <t>Bergsjön, Bergsjön, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483472</v>
+        <v>475023</v>
       </c>
       <c r="R56" t="n">
-        <v>6512384</v>
+        <v>6512397</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6911,42 +6922,37 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Laxå</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Västergötland</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Tived</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6961,69 +6967,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665086</t>
+          <t>https://artportalen.se/Sighting/136307714</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>92087603</v>
+        <v>134665086</v>
       </c>
       <c r="B57" t="n">
-        <v>56522</v>
+        <v>99142</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>206004</v>
+        <v>6010639</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blodnycklar × fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. cruenta × maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tiveden, Vg</t>
+          <t>Olshammar, Nrk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476171</v>
+        <v>483472</v>
       </c>
       <c r="R57" t="n">
-        <v>6510583</v>
+        <v>6512384</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7032,37 +7034,42 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Laxå</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Västergötland</t>
+          <t>Närke</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Tived</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7077,16 +7084,132 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>David van der Spoel</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>David van der Spoel</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665086</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>92087603</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tiveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>476171</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6510583</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/92087603</t>
         </is>
@@ -7150,6 +7273,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -6132,7 +6132,7 @@
         <v>136983633</v>
       </c>
       <c r="B50" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -6132,7 +6132,7 @@
         <v>136983633</v>
       </c>
       <c r="B50" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -6159,16 +6159,8 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -6132,7 +6132,7 @@
         <v>136983633</v>
       </c>
       <c r="B50" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -6132,7 +6132,7 @@
         <v>136983633</v>
       </c>
       <c r="B50" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -6132,7 +6132,7 @@
         <v>136983633</v>
       </c>
       <c r="B50" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
